--- a/Result/profitability/6147.xlsx
+++ b/Result/profitability/6147.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>22.645</v>
+        <v>23.3125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.83625</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>21.375</v>
+        <v>22.17125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.71</v>
+        <v>0.7575</v>
       </c>
       <c r="N4" t="n">
-        <v>19.965</v>
+        <v>20.8825</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.465</v>
+        <v>0.55625</v>
       </c>
       <c r="N5" t="n">
-        <v>16.2325</v>
+        <v>17.46125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.32625</v>
+        <v>0.34</v>
       </c>
       <c r="N6" t="n">
-        <v>10.98625</v>
+        <v>12.13875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.26</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2125</v>
+        <v>0.2325</v>
       </c>
       <c r="N7" t="n">
-        <v>10.37</v>
+        <v>11.5125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.03</v>
       </c>
       <c r="M8" t="n">
-        <v>0.20125</v>
+        <v>0.2875</v>
       </c>
       <c r="N8" t="n">
-        <v>10.8775</v>
+        <v>11.7325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,16 +1403,16 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6632</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4623</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1278</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>93</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1371</v>
+      </c>
+      <c r="K75" t="n">
+        <v>950</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0225</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.169491525423729</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2915601023017902</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.327272727272727</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.830000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4802149487054226</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
